--- a/华风数据-初审-itss3/新版-补充清单(1).xlsx
+++ b/华风数据-初审-itss3/新版-补充清单(1).xlsx
@@ -122,10 +122,10 @@
     <t>刘文桂</t>
   </si>
   <si>
-    <t>产品产品质量部门</t>
-  </si>
-  <si>
-    <t>产品产品产品质量部</t>
+    <t>产品质量部门</t>
+  </si>
+  <si>
+    <t>产品产品质量部</t>
   </si>
   <si>
     <t>熊振翔</t>
@@ -859,7 +859,7 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="78">
+  <cellStyleXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
       <protection/>
@@ -893,6 +893,11 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment/>
     </xf>
@@ -1106,7 +1111,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="64">
+  <cellStyles count="69">
     <cellStyle name="Normal" xfId="0"/>
     <cellStyle name="Percent" xfId="15"/>
     <cellStyle name="Currency" xfId="16"/>
@@ -1123,54 +1128,59 @@
     <cellStyle name="Currency [0]" xfId="27"/>
     <cellStyle name="Comma" xfId="28"/>
     <cellStyle name="Comma [0]" xfId="29"/>
-    <cellStyle name="千位分隔" xfId="30"/>
-    <cellStyle name="货币" xfId="31"/>
-    <cellStyle name="百分比" xfId="32"/>
-    <cellStyle name="千位分隔[0]" xfId="33"/>
-    <cellStyle name="货币[0]" xfId="34"/>
-    <cellStyle name="超链接" xfId="35"/>
-    <cellStyle name="已访问的超链接" xfId="36"/>
-    <cellStyle name="注释" xfId="37"/>
-    <cellStyle name="警告文本" xfId="38"/>
-    <cellStyle name="标题" xfId="39"/>
-    <cellStyle name="解释性文本" xfId="40"/>
-    <cellStyle name="标题 1" xfId="41"/>
-    <cellStyle name="标题 2" xfId="42"/>
-    <cellStyle name="标题 3" xfId="43"/>
-    <cellStyle name="标题 4" xfId="44"/>
-    <cellStyle name="输入" xfId="45"/>
-    <cellStyle name="输出" xfId="46"/>
-    <cellStyle name="计算" xfId="47"/>
-    <cellStyle name="检查单元格" xfId="48"/>
-    <cellStyle name="链接单元格" xfId="49"/>
-    <cellStyle name="汇总" xfId="50"/>
-    <cellStyle name="好" xfId="51"/>
-    <cellStyle name="差" xfId="52"/>
-    <cellStyle name="适中" xfId="53"/>
-    <cellStyle name="强调文字颜色 1" xfId="54"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="55"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="56"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="57"/>
-    <cellStyle name="强调文字颜色 2" xfId="58"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="59"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="60"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="61"/>
-    <cellStyle name="强调文字颜色 3" xfId="62"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="63"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="64"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="65"/>
-    <cellStyle name="强调文字颜色 4" xfId="66"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="67"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="68"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="69"/>
-    <cellStyle name="强调文字颜色 5" xfId="70"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="71"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="72"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="73"/>
-    <cellStyle name="强调文字颜色 6" xfId="74"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="75"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="76"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="77"/>
+    <cellStyle name="Percent" xfId="30"/>
+    <cellStyle name="Currency" xfId="31"/>
+    <cellStyle name="Currency [0]" xfId="32"/>
+    <cellStyle name="Comma" xfId="33"/>
+    <cellStyle name="Comma [0]" xfId="34"/>
+    <cellStyle name="千位分隔" xfId="35"/>
+    <cellStyle name="货币" xfId="36"/>
+    <cellStyle name="百分比" xfId="37"/>
+    <cellStyle name="千位分隔[0]" xfId="38"/>
+    <cellStyle name="货币[0]" xfId="39"/>
+    <cellStyle name="超链接" xfId="40"/>
+    <cellStyle name="已访问的超链接" xfId="41"/>
+    <cellStyle name="注释" xfId="42"/>
+    <cellStyle name="警告文本" xfId="43"/>
+    <cellStyle name="标题" xfId="44"/>
+    <cellStyle name="解释性文本" xfId="45"/>
+    <cellStyle name="标题 1" xfId="46"/>
+    <cellStyle name="标题 2" xfId="47"/>
+    <cellStyle name="标题 3" xfId="48"/>
+    <cellStyle name="标题 4" xfId="49"/>
+    <cellStyle name="输入" xfId="50"/>
+    <cellStyle name="输出" xfId="51"/>
+    <cellStyle name="计算" xfId="52"/>
+    <cellStyle name="检查单元格" xfId="53"/>
+    <cellStyle name="链接单元格" xfId="54"/>
+    <cellStyle name="汇总" xfId="55"/>
+    <cellStyle name="好" xfId="56"/>
+    <cellStyle name="差" xfId="57"/>
+    <cellStyle name="适中" xfId="58"/>
+    <cellStyle name="强调文字颜色 1" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="60"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="61"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="62"/>
+    <cellStyle name="强调文字颜色 2" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="64"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="65"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="66"/>
+    <cellStyle name="强调文字颜色 3" xfId="67"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="68"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="69"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="70"/>
+    <cellStyle name="强调文字颜色 4" xfId="71"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="72"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="73"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="74"/>
+    <cellStyle name="强调文字颜色 5" xfId="75"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="76"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="77"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="78"/>
+    <cellStyle name="强调文字颜色 6" xfId="79"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="80"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="81"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="82"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
@@ -1827,7 +1837,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1"/>
-        <a:srcRect l="7621"/>
+        <a:srcRect l="7620"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1868,7 +1878,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId2"/>
-        <a:srcRect r="23396"/>
+        <a:srcRect r="23394"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1909,7 +1919,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId3"/>
-        <a:srcRect l="4876" t="5352"/>
+        <a:srcRect l="4875" t="5351"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1995,7 +2005,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId2"/>
-        <a:srcRect r="20359"/>
+        <a:srcRect r="20358"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
